--- a/public/converted/schet-treid-resurs-05-10-v-zagruzku.xlsx
+++ b/public/converted/schet-treid-resurs-05-10-v-zagruzku.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$1:$E$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Товары'!$A$1:$F$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,14 +424,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,15 +448,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Цена</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
@@ -472,15 +478,20 @@
           <t>4610509420351</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>17816.7</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 D Inverter NoFrost Dark Grey Soft Close</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>17816.7</v>
       </c>
+      <c r="F2" s="4" t="n">
+        <v>17816.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -493,15 +504,20 @@
           <t>4393720607274</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>20786.7</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2010 Full NoFrost Inverter Black</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>20786.7</v>
       </c>
+      <c r="F3" s="4" t="n">
+        <v>20786.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -514,15 +530,20 @@
           <t>4393720600497</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>5111.7</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Винный холодильник Weissgauff WWC-08 Bottle</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>5111.7</v>
       </c>
+      <c r="F4" s="4" t="n">
+        <v>5111.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -535,15 +556,20 @@
           <t>4393720600510</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>7751.7</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Винный холодильник Weissgauff WWC-18 Bottle</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>7751.7</v>
       </c>
+      <c r="F5" s="4" t="n">
+        <v>7751.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -556,15 +582,20 @@
           <t>4393720474630</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>21116.7</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Винный холодильник Weissgauff WWC-46 DB DualZone</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>21116.7</v>
       </c>
+      <c r="F6" s="4" t="n">
+        <v>21116.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -577,15 +608,20 @@
           <t>4393720474616</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>12536.7</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Винный холодильник Weissgauff WWC-7 B</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>12536.7</v>
       </c>
+      <c r="F7" s="4" t="n">
+        <v>12536.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -598,15 +634,20 @@
           <t>4393720609742</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>5936.7</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Водонагреватель накопительный Weissgauff WWH 50D Touch Enamel Tank</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>5936.7</v>
       </c>
+      <c r="F8" s="4" t="n">
+        <v>5936.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -619,15 +660,20 @@
           <t>4393720609681</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>5045.7</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Водонагреватель накопительный Weissgauff WWH 80 Enamel Tank</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>5045.7</v>
       </c>
+      <c r="F9" s="4" t="n">
+        <v>5045.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -640,13 +686,18 @@
           <t>4393720604778</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Box 1400 Island BL</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>6596.7</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>13193.4</v>
       </c>
     </row>
@@ -661,15 +712,20 @@
           <t>4393720606291</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>6266.7</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff BOX 900 Remove Touch Black Glass</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>6266.7</v>
       </c>
+      <c r="F11" s="4" t="n">
+        <v>6266.7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -682,15 +738,20 @@
           <t>4393720463979</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>6926.7</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Gracia WH</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>6926.7</v>
       </c>
+      <c r="F12" s="4" t="n">
+        <v>6926.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -703,13 +764,18 @@
           <t>4393720604587</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff TEL 450 White Glass</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>2801.7</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>14008.5</v>
       </c>
     </row>
@@ -724,15 +790,20 @@
           <t>4393720604662</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>3461.7</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Вытяжка Weissgauff Yota 500 Touch White Glass</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>3461.7</v>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>3461.7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -745,13 +816,18 @@
           <t>4393720608721</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 430 BFh</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>3956.7</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>7913.4</v>
       </c>
     </row>
@@ -766,15 +842,20 @@
           <t>4393720472476</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>3626.7</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 430 WGH</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>3626.7</v>
       </c>
+      <c r="F16" s="4" t="n">
+        <v>3626.7</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -787,13 +868,18 @@
           <t>4393720608769</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 640 BFh</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>4451.7</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>8903.4</v>
       </c>
     </row>
@@ -808,15 +894,20 @@
           <t>4393720472513</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>4286.7</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 640 BG</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>4286.7</v>
       </c>
+      <c r="F18" s="4" t="n">
+        <v>4286.7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -829,15 +920,20 @@
           <t>4393720600565</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>4451.7</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 640 BGh</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>4451.7</v>
       </c>
+      <c r="F19" s="4" t="n">
+        <v>4451.7</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -850,13 +946,18 @@
           <t>4393720608776</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 641 BFh</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>4451.7</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>13355.1</v>
       </c>
     </row>
@@ -871,15 +972,20 @@
           <t>4393720608783</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>4781.7</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HG 641 WFh</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>4781.7</v>
       </c>
+      <c r="F21" s="4" t="n">
+        <v>4781.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -892,15 +998,20 @@
           <t>4393720475262</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>2966.7</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 320 WGR</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>2966.7</v>
       </c>
+      <c r="F22" s="4" t="n">
+        <v>2966.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -913,15 +1024,20 @@
           <t>4670239260634</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>4451.7</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 451 BFK</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>4451.7</v>
       </c>
+      <c r="F23" s="4" t="n">
+        <v>4451.7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -934,15 +1050,20 @@
           <t>4393720447870</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>3956.7</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 451 BGh</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>3956.7</v>
       </c>
+      <c r="F24" s="4" t="n">
+        <v>3956.7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -955,15 +1076,20 @@
           <t>4393720450573</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>4451.7</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 451 WFh</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>4451.7</v>
       </c>
+      <c r="F25" s="4" t="n">
+        <v>4451.7</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -976,13 +1102,18 @@
           <t>4393720450580</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 451 XFh</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="E26" s="4" t="n">
         <v>4451.7</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="F26" s="4" t="n">
         <v>8903.4</v>
       </c>
     </row>
@@ -997,15 +1128,20 @@
           <t>4670239260665</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>4451.7</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 451 XFK</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>4451.7</v>
       </c>
+      <c r="F27" s="4" t="n">
+        <v>4451.7</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1018,15 +1154,20 @@
           <t>4393720439714</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>4781.7</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 640 BG</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>4781.7</v>
       </c>
+      <c r="F28" s="4" t="n">
+        <v>4781.7</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1039,13 +1180,18 @@
           <t>4393720473749</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 640 BGB</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="E29" s="4" t="n">
         <v>5276.7</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="F29" s="4" t="n">
         <v>10553.4</v>
       </c>
     </row>
@@ -1060,13 +1206,18 @@
           <t>4670239260788</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 BEBEH MATT METAL</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="E30" s="4" t="n">
         <v>5771.7</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="F30" s="4" t="n">
         <v>11543.4</v>
       </c>
     </row>
@@ -1081,13 +1232,18 @@
           <t>4393720445432</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 BGh</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="E31" s="4" t="n">
         <v>5606.7</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>16820.1</v>
       </c>
     </row>
@@ -1102,15 +1258,20 @@
           <t>4670239260801</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>5441.7</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 BGSH</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>5441.7</v>
       </c>
+      <c r="F32" s="4" t="n">
+        <v>5441.7</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1123,15 +1284,20 @@
           <t>4670239260702</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>5771.7</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 BGSK Nano Matt Glass</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E33" s="4" t="n">
         <v>5771.7</v>
       </c>
+      <c r="F33" s="4" t="n">
+        <v>5771.7</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1144,13 +1310,18 @@
           <t>4393720600213</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 BGV</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="E34" s="4" t="n">
         <v>5441.7</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="F34" s="4" t="n">
         <v>10883.4</v>
       </c>
     </row>
@@ -1165,15 +1336,20 @@
           <t>4393720477709</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>5936.7</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 BV Nano Matt Glass</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E35" s="4" t="n">
         <v>5936.7</v>
       </c>
+      <c r="F35" s="4" t="n">
+        <v>5936.7</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1186,13 +1362,18 @@
           <t>4393720445456</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 641 Xh</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>5111.7</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="F36" s="4" t="n">
         <v>20446.8</v>
       </c>
     </row>
@@ -1207,15 +1388,20 @@
           <t>4393720609407</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>8411.700000000001</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Газовая панель Weissgauff HGG 642 BGW Double Wok Timer</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E37" s="4" t="n">
         <v>8411.700000000001</v>
       </c>
+      <c r="F37" s="4" t="n">
+        <v>8411.700000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1228,15 +1414,20 @@
           <t>4640563532103</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>7421.7</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Дегидратор Weissgauff WDH 320 Digital Dry Pro</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E38" s="4" t="n">
         <v>7421.7</v>
       </c>
+      <c r="F38" s="4" t="n">
+        <v>7421.7</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1249,15 +1440,20 @@
           <t>4393720606154</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>6761.7</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 104 X</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E39" s="4" t="n">
         <v>6761.7</v>
       </c>
+      <c r="F39" s="4" t="n">
+        <v>6761.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1270,15 +1466,20 @@
           <t>4393720611271</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>6596.7</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 106 PMB Easy Clean</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E40" s="4" t="n">
         <v>6596.7</v>
       </c>
+      <c r="F40" s="4" t="n">
+        <v>6596.7</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1291,15 +1492,20 @@
           <t>4393720478065</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>8411.700000000001</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 208 PDB Steam Clean</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E41" s="4" t="n">
         <v>8411.700000000001</v>
       </c>
+      <c r="F41" s="4" t="n">
+        <v>8411.700000000001</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1312,15 +1518,20 @@
           <t>4393720478072</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>8411.700000000001</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 208 PDW Steam Clean</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E42" s="4" t="n">
         <v>8411.700000000001</v>
       </c>
+      <c r="F42" s="4" t="n">
+        <v>8411.700000000001</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1333,15 +1544,20 @@
           <t>4393720478089</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>8411.700000000001</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 208 PDX Steam Clean</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E43" s="4" t="n">
         <v>8411.700000000001</v>
       </c>
+      <c r="F43" s="4" t="n">
+        <v>8411.700000000001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1354,13 +1570,18 @@
           <t>4393720473633</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 262 PMW</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="E44" s="4" t="n">
         <v>8081.7</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="F44" s="4" t="n">
         <v>16163.4</v>
       </c>
     </row>
@@ -1375,15 +1596,20 @@
           <t>4393720473657</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>8906.700000000001</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 362 PDW</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E45" s="4" t="n">
         <v>8906.700000000001</v>
       </c>
+      <c r="F45" s="4" t="n">
+        <v>8906.700000000001</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1396,13 +1622,18 @@
           <t>4393720439400</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 691 PDB</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="E46" s="4" t="n">
         <v>9896.700000000001</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="F46" s="4" t="n">
         <v>19793.4</v>
       </c>
     </row>
@@ -1417,15 +1648,20 @@
           <t>4393720606499</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>13691.7</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 699 PDB Digital Smart Soft Close</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>13691.7</v>
       </c>
+      <c r="F47" s="4" t="n">
+        <v>13691.7</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1438,15 +1674,20 @@
           <t>4393720600367</t>
         </is>
       </c>
-      <c r="C48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>11876.7</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOM 741 PDB Black Edition</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E48" s="4" t="n">
         <v>11876.7</v>
       </c>
+      <c r="F48" s="4" t="n">
+        <v>11876.7</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1459,15 +1700,20 @@
           <t>4602807509258</t>
         </is>
       </c>
-      <c r="C49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>5771.7</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOV 166 LB</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E49" s="4" t="n">
         <v>5771.7</v>
       </c>
+      <c r="F49" s="4" t="n">
+        <v>5771.7</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1480,13 +1726,18 @@
           <t>4393720442653</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOV 29 PDB</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="E50" s="4" t="n">
         <v>8741.700000000001</v>
       </c>
-      <c r="E50" s="4" t="n">
+      <c r="F50" s="4" t="n">
         <v>17483.4</v>
       </c>
     </row>
@@ -1501,15 +1752,20 @@
           <t>4393720468509</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>10391.7</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOV 691 PDW</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>10391.7</v>
       </c>
+      <c r="F51" s="4" t="n">
+        <v>10391.7</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1522,15 +1778,20 @@
           <t>4393720463054</t>
         </is>
       </c>
-      <c r="C52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>10721.7</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff EOY 451 PDW</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>10721.7</v>
       </c>
+      <c r="F52" s="4" t="n">
+        <v>10721.7</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1543,15 +1804,20 @@
           <t>4393720606765</t>
         </is>
       </c>
-      <c r="C53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>10061.7</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff OE 459 PDB Black Edition</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E53" s="4" t="n">
         <v>10061.7</v>
       </c>
+      <c r="F53" s="4" t="n">
+        <v>10061.7</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1564,15 +1830,20 @@
           <t>4393720606772</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>8906.700000000001</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Духовой шкаф Weissgauff OE 459 SDB Black Edition</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E54" s="4" t="n">
         <v>8906.700000000001</v>
       </c>
+      <c r="F54" s="4" t="n">
+        <v>8906.700000000001</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1585,13 +1856,18 @@
           <t>4393720603573</t>
         </is>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff BMWO-206</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="E55" s="4" t="n">
         <v>5441.7</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="F55" s="4" t="n">
         <v>16325.1</v>
       </c>
     </row>
@@ -1606,13 +1882,18 @@
           <t>4393720475194</t>
         </is>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-2012 Grill</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="E56" s="4" t="n">
         <v>5936.7</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="F56" s="4" t="n">
         <v>23746.8</v>
       </c>
     </row>
@@ -1627,15 +1908,20 @@
           <t>4393720603559</t>
         </is>
       </c>
-      <c r="C57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>5441.7</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-2016 BGL</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E57" s="4" t="n">
         <v>5441.7</v>
       </c>
+      <c r="F57" s="4" t="n">
+        <v>5441.7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1648,13 +1934,18 @@
           <t>4393720475170</t>
         </is>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-2016 Grill</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="E58" s="4" t="n">
         <v>5441.7</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="F58" s="4" t="n">
         <v>21766.8</v>
       </c>
     </row>
@@ -1669,15 +1960,20 @@
           <t>4393720442820</t>
         </is>
       </c>
-      <c r="C59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>8246.700000000001</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-202</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>8246.700000000001</v>
       </c>
+      <c r="F59" s="4" t="n">
+        <v>8246.700000000001</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1690,13 +1986,18 @@
           <t>4393720605447</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-206 B</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="E60" s="4" t="n">
         <v>7421.7</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="F60" s="4" t="n">
         <v>37108.5</v>
       </c>
     </row>
@@ -1711,15 +2012,20 @@
           <t>4393720477044</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>6266.7</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-206 Compact</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E61" s="4" t="n">
         <v>6266.7</v>
       </c>
+      <c r="F61" s="4" t="n">
+        <v>6266.7</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1732,13 +2038,18 @@
           <t>4393720477051</t>
         </is>
       </c>
-      <c r="C62" s="3" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-206 Compact Grill</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="E62" s="4" t="n">
         <v>6596.7</v>
       </c>
-      <c r="E62" s="4" t="n">
+      <c r="F62" s="4" t="n">
         <v>26386.8</v>
       </c>
     </row>
@@ -1753,15 +2064,20 @@
           <t>4393720472315</t>
         </is>
       </c>
-      <c r="C63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>7421.7</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-220 WG Grill</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E63" s="4" t="n">
         <v>7421.7</v>
       </c>
+      <c r="F63" s="4" t="n">
+        <v>7421.7</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1774,15 +2090,20 @@
           <t>4393720459682</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>10556.7</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-252</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E64" s="4" t="n">
         <v>10556.7</v>
       </c>
+      <c r="F64" s="4" t="n">
+        <v>10556.7</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1795,15 +2116,20 @@
           <t>4393720605454</t>
         </is>
       </c>
-      <c r="C65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>12206.7</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-252 TSW</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E65" s="4" t="n">
         <v>12206.7</v>
       </c>
+      <c r="F65" s="4" t="n">
+        <v>12206.7</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1816,13 +2142,18 @@
           <t>4393720605065</t>
         </is>
       </c>
-      <c r="C66" s="3" t="n">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-256 Full Touch</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="E66" s="4" t="n">
         <v>8081.7</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="F66" s="4" t="n">
         <v>16163.4</v>
       </c>
     </row>
@@ -1837,15 +2168,20 @@
           <t>4393720606581</t>
         </is>
       </c>
-      <c r="C67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>12536.7</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-256 TSB Matt Edition</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E67" s="4" t="n">
         <v>12536.7</v>
       </c>
+      <c r="F67" s="4" t="n">
+        <v>12536.7</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1858,15 +2194,20 @@
           <t>4393720604112</t>
         </is>
       </c>
-      <c r="C68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>5111.7</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-452 D</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>5111.7</v>
       </c>
+      <c r="F68" s="4" t="n">
+        <v>5111.7</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1879,13 +2220,18 @@
           <t>4393720604082</t>
         </is>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-456</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="E69" s="4" t="n">
         <v>4946.7</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="F69" s="4" t="n">
         <v>9893.4</v>
       </c>
     </row>
@@ -1900,13 +2246,18 @@
           <t>4393720604099</t>
         </is>
       </c>
-      <c r="C70" s="3" t="n">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-456 D</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="E70" s="4" t="n">
         <v>5276.7</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="F70" s="4" t="n">
         <v>15830.1</v>
       </c>
     </row>
@@ -1921,13 +2272,18 @@
           <t>4393720602460</t>
         </is>
       </c>
-      <c r="C71" s="3" t="n">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-620 B Grill</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="E71" s="4" t="n">
         <v>5936.7</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="F71" s="4" t="n">
         <v>23746.8</v>
       </c>
     </row>
@@ -1942,15 +2298,20 @@
           <t>4393720604754</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>7256.7</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-620 BG Grill Matt Edition</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E72" s="4" t="n">
         <v>7256.7</v>
       </c>
+      <c r="F72" s="4" t="n">
+        <v>7256.7</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -1963,15 +2324,20 @@
           <t>4393720605058</t>
         </is>
       </c>
-      <c r="C73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>6926.7</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-620 Compact Touch</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E73" s="4" t="n">
         <v>6926.7</v>
       </c>
+      <c r="F73" s="4" t="n">
+        <v>6926.7</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -1984,13 +2350,18 @@
           <t>4393720470878</t>
         </is>
       </c>
-      <c r="C74" s="3" t="n">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Микроволновая печь Weissgauff HMT-625 Grill</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="E74" s="4" t="n">
         <v>7421.7</v>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="F74" s="4" t="n">
         <v>29686.8</v>
       </c>
     </row>
@@ -2005,15 +2376,20 @@
           <t>4393720609476</t>
         </is>
       </c>
-      <c r="C75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>3263.7</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Мини-печь Weissgauff WMR 30P Black</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E75" s="4" t="n">
         <v>3263.7</v>
       </c>
+      <c r="F75" s="4" t="n">
+        <v>3263.7</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2026,15 +2402,20 @@
           <t>4393720609469</t>
         </is>
       </c>
-      <c r="C76" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>3560.7</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Мини-печь Weissgauff WMR 40 Black</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E76" s="4" t="n">
         <v>3560.7</v>
       </c>
+      <c r="F76" s="4" t="n">
+        <v>3560.7</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2047,13 +2428,18 @@
           <t>4393720609001</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Морозильник Weissgauff WFH-150 Inverter</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="E77" s="4" t="n">
         <v>8396.5</v>
       </c>
-      <c r="E77" s="4" t="n">
+      <c r="F77" s="4" t="n">
         <v>25189.5</v>
       </c>
     </row>
@@ -2068,15 +2454,20 @@
           <t>4393720609025</t>
         </is>
       </c>
-      <c r="C78" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>11021.5</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Морозильник Weissgauff WFH-250 Inverter</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>11021.5</v>
       </c>
+      <c r="F78" s="4" t="n">
+        <v>11021.5</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2089,15 +2480,20 @@
           <t>4393720609049</t>
         </is>
       </c>
-      <c r="C79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>17321.5</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Морозильник Weissgauff WFH-360 Inverter</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>17321.5</v>
       </c>
+      <c r="F79" s="4" t="n">
+        <v>17321.5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2110,15 +2506,20 @@
           <t>4393720607397</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>9271.5</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Морозильник Weissgauff WRF-80 Defrost Black</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E80" s="4" t="n">
         <v>9271.5</v>
       </c>
+      <c r="F80" s="4" t="n">
+        <v>9271.5</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2131,13 +2532,18 @@
           <t>4393720607410</t>
         </is>
       </c>
-      <c r="C81" s="3" t="n">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Морозильник Weissgauff WRF-80 Defrost White</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D81" s="4" t="n">
+      <c r="E81" s="4" t="n">
         <v>8921.5</v>
       </c>
-      <c r="E81" s="4" t="n">
+      <c r="F81" s="4" t="n">
         <v>17843</v>
       </c>
     </row>
@@ -2152,13 +2558,18 @@
           <t>4393720477860</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4026</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D82" s="4" t="n">
+      <c r="E82" s="4" t="n">
         <v>9401.700000000001</v>
       </c>
-      <c r="E82" s="4" t="n">
+      <c r="F82" s="4" t="n">
         <v>18803.4</v>
       </c>
     </row>
@@ -2173,15 +2584,20 @@
           <t>4393720609155</t>
         </is>
       </c>
-      <c r="C83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" s="4" t="n">
-        <v>11876.7</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4535 D Inverter AutoOpen Timer Floor</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E83" s="4" t="n">
         <v>11876.7</v>
       </c>
+      <c r="F83" s="4" t="n">
+        <v>11876.7</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2194,13 +2610,18 @@
           <t>4393720477891</t>
         </is>
       </c>
-      <c r="C84" s="3" t="n">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4536 D</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D84" s="4" t="n">
+      <c r="E84" s="4" t="n">
         <v>9896.700000000001</v>
       </c>
-      <c r="E84" s="4" t="n">
+      <c r="F84" s="4" t="n">
         <v>19793.4</v>
       </c>
     </row>
@@ -2215,15 +2636,20 @@
           <t>4393720468332</t>
         </is>
       </c>
-      <c r="C85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>10391.7</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4537</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E85" s="4" t="n">
         <v>10391.7</v>
       </c>
+      <c r="F85" s="4" t="n">
+        <v>10391.7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2236,15 +2662,20 @@
           <t>4393720610342</t>
         </is>
       </c>
-      <c r="C86" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="4" t="n">
-        <v>10721.7</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 4538 Timer Floor</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E86" s="4" t="n">
         <v>10721.7</v>
       </c>
+      <c r="F86" s="4" t="n">
+        <v>10721.7</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2257,15 +2688,20 @@
           <t>4393720600589</t>
         </is>
       </c>
-      <c r="C87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D87" s="4" t="n">
-        <v>13691.7</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff BDW 6038 D Autoopen</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E87" s="4" t="n">
         <v>13691.7</v>
       </c>
+      <c r="F87" s="4" t="n">
+        <v>13691.7</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2278,13 +2714,18 @@
           <t>4393720447924</t>
         </is>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 4015</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D88" s="4" t="n">
+      <c r="E88" s="4" t="n">
         <v>10721.7</v>
       </c>
-      <c r="E88" s="4" t="n">
+      <c r="F88" s="4" t="n">
         <v>32165.1</v>
       </c>
     </row>
@@ -2299,15 +2740,20 @@
           <t>4393720459743</t>
         </is>
       </c>
-      <c r="C89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>6596.7</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 4035</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>6596.7</v>
       </c>
+      <c r="F89" s="4" t="n">
+        <v>6596.7</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2320,15 +2766,20 @@
           <t>4393720475927</t>
         </is>
       </c>
-      <c r="C90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>14846.7</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 4539 Inverter Touch AutoOpen Black</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E90" s="4" t="n">
         <v>14846.7</v>
       </c>
+      <c r="F90" s="4" t="n">
+        <v>14846.7</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2341,15 +2792,20 @@
           <t>4393720475934</t>
         </is>
       </c>
-      <c r="C91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" s="4" t="n">
-        <v>14846.7</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 4539 Inverter Touch AutoOpen White</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E91" s="4" t="n">
         <v>14846.7</v>
       </c>
+      <c r="F91" s="4" t="n">
+        <v>14846.7</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2362,15 +2818,20 @@
           <t>4393720603443</t>
         </is>
       </c>
-      <c r="C92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" s="4" t="n">
-        <v>13361.7</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 6038 Autoopen</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E92" s="4" t="n">
         <v>13361.7</v>
       </c>
+      <c r="F92" s="4" t="n">
+        <v>13361.7</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2383,13 +2844,18 @@
           <t>4393720603962</t>
         </is>
       </c>
-      <c r="C93" s="3" t="n">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 6038 X Inverter</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D93" s="4" t="n">
+      <c r="E93" s="4" t="n">
         <v>14021.7</v>
       </c>
-      <c r="E93" s="4" t="n">
+      <c r="F93" s="4" t="n">
         <v>28043.4</v>
       </c>
     </row>
@@ -2404,15 +2870,20 @@
           <t>4393720604181</t>
         </is>
       </c>
-      <c r="C94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" s="4" t="n">
-        <v>16991.7</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 996 Touch Inverter Dual Fan Dry</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>16991.7</v>
       </c>
+      <c r="F94" s="4" t="n">
+        <v>16991.7</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2425,15 +2896,20 @@
           <t>4393720604198</t>
         </is>
       </c>
-      <c r="C95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>16991.7</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 998 Touch Inverter Dual Fan Dry</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E95" s="4" t="n">
         <v>16991.7</v>
       </c>
+      <c r="F95" s="4" t="n">
+        <v>16991.7</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2446,15 +2922,20 @@
           <t>4393720604204</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" s="4" t="n">
-        <v>16166.7</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff DW 999 Touch Inverter Dual Fan Dry</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E96" s="4" t="n">
         <v>16166.7</v>
       </c>
+      <c r="F96" s="4" t="n">
+        <v>16166.7</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2467,15 +2948,20 @@
           <t>4393720447900</t>
         </is>
       </c>
-      <c r="C97" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" s="4" t="n">
-        <v>7421.7</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4006</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E97" s="4" t="n">
         <v>7421.7</v>
       </c>
+      <c r="F97" s="4" t="n">
+        <v>7421.7</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2488,15 +2974,20 @@
           <t>4393720458876</t>
         </is>
       </c>
-      <c r="C98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" s="4" t="n">
-        <v>9236.700000000001</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4006 D</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E98" s="4" t="n">
         <v>9236.700000000001</v>
       </c>
+      <c r="F98" s="4" t="n">
+        <v>9236.700000000001</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2509,15 +3000,20 @@
           <t>4393720458883</t>
         </is>
       </c>
-      <c r="C99" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" s="4" t="n">
-        <v>9566.700000000001</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4006 S</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E99" s="4" t="n">
         <v>9566.700000000001</v>
       </c>
+      <c r="F99" s="4" t="n">
+        <v>9566.700000000001</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2530,15 +3026,20 @@
           <t>4393720447917</t>
         </is>
       </c>
-      <c r="C100" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" s="4" t="n">
-        <v>8741.700000000001</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4017 D</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E100" s="4" t="n">
         <v>8741.700000000001</v>
       </c>
+      <c r="F100" s="4" t="n">
+        <v>8741.700000000001</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2551,15 +3052,20 @@
           <t>4393720450955</t>
         </is>
       </c>
-      <c r="C101" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" s="4" t="n">
-        <v>8741.700000000001</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Посудомоечная машина Weissgauff TDW 4017 DS</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E101" s="4" t="n">
         <v>8741.700000000001</v>
       </c>
+      <c r="F101" s="4" t="n">
+        <v>8741.700000000001</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2572,15 +3078,20 @@
           <t>4393720608394</t>
         </is>
       </c>
-      <c r="C102" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" s="4" t="n">
-        <v>12596.5</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 39107 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E102" s="4" t="n">
         <v>12596.5</v>
       </c>
+      <c r="F102" s="4" t="n">
+        <v>12596.5</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2593,13 +3104,18 @@
           <t>4393720605782</t>
         </is>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 40106 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D103" s="4" t="n">
+      <c r="E103" s="4" t="n">
         <v>11721.5</v>
       </c>
-      <c r="E103" s="4" t="n">
+      <c r="F103" s="4" t="n">
         <v>46886</v>
       </c>
     </row>
@@ -2614,15 +3130,20 @@
           <t>4393720606260</t>
         </is>
       </c>
-      <c r="C104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>14521.5</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4106 D Deep Grey</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E104" s="4" t="n">
         <v>14521.5</v>
       </c>
+      <c r="F104" s="4" t="n">
+        <v>14521.5</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2635,15 +3156,20 @@
           <t>4393720605676</t>
         </is>
       </c>
-      <c r="C105" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" s="4" t="n">
-        <v>12071.5</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 41106 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E105" s="4" t="n">
         <v>12071.5</v>
       </c>
+      <c r="F105" s="4" t="n">
+        <v>12071.5</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2656,13 +3182,18 @@
           <t>4393720607861</t>
         </is>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4506 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D106" s="4" t="n">
+      <c r="E106" s="4" t="n">
         <v>11546.5</v>
       </c>
-      <c r="E106" s="4" t="n">
+      <c r="F106" s="4" t="n">
         <v>23093</v>
       </c>
     </row>
@@ -2677,15 +3208,20 @@
           <t>4393720473282</t>
         </is>
       </c>
-      <c r="C107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" s="4" t="n">
-        <v>11721.5</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4506 LED</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E107" s="4" t="n">
         <v>11721.5</v>
       </c>
+      <c r="F107" s="4" t="n">
+        <v>11721.5</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2698,13 +3234,18 @@
           <t>4393720610953</t>
         </is>
       </c>
-      <c r="C108" s="3" t="n">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 45106 Color Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D108" s="4" t="n">
+      <c r="E108" s="4" t="n">
         <v>13646.5</v>
       </c>
-      <c r="E108" s="4" t="n">
+      <c r="F108" s="4" t="n">
         <v>27293</v>
       </c>
     </row>
@@ -2719,15 +3260,20 @@
           <t>4393720610960</t>
         </is>
       </c>
-      <c r="C109" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D109" s="4" t="n">
-        <v>14171.5</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 45106 Color Touch Inverter Steam Dark Grey</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E109" s="4" t="n">
         <v>14171.5</v>
       </c>
+      <c r="F109" s="4" t="n">
+        <v>14171.5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2740,15 +3286,20 @@
           <t>4393720607199</t>
         </is>
       </c>
-      <c r="C110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" s="4" t="n">
-        <v>20471.5</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 45148 Color Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E110" s="4" t="n">
         <v>20471.5</v>
       </c>
+      <c r="F110" s="4" t="n">
+        <v>20471.5</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2761,15 +3312,20 @@
           <t>4393720600824</t>
         </is>
       </c>
-      <c r="C111" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" s="4" t="n">
-        <v>15746.5</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4627 Touch Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E111" s="4" t="n">
         <v>15746.5</v>
       </c>
+      <c r="F111" s="4" t="n">
+        <v>15746.5</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2782,15 +3338,20 @@
           <t>4393720605584</t>
         </is>
       </c>
-      <c r="C112" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D112" s="4" t="n">
-        <v>16796.5</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 4627 Touch Inverter Steam Grey</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E112" s="4" t="n">
         <v>16796.5</v>
       </c>
+      <c r="F112" s="4" t="n">
+        <v>16796.5</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2803,15 +3364,20 @@
           <t>4393720602781</t>
         </is>
       </c>
-      <c r="C113" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D113" s="4" t="n">
-        <v>16796.5</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 47147 DC Inverter Steam Black</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E113" s="4" t="n">
         <v>16796.5</v>
       </c>
+      <c r="F113" s="4" t="n">
+        <v>16796.5</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2824,15 +3390,20 @@
           <t>4393720605706</t>
         </is>
       </c>
-      <c r="C114" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" s="4" t="n">
-        <v>14871.5</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 48128 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E114" s="4" t="n">
         <v>14871.5</v>
       </c>
+      <c r="F114" s="4" t="n">
+        <v>14871.5</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2845,15 +3416,20 @@
           <t>4393720602545</t>
         </is>
       </c>
-      <c r="C115" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D115" s="4" t="n">
-        <v>26771.5</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 58411 Direct Drive Inverter Premium Steam Grey</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E115" s="4" t="n">
         <v>26771.5</v>
       </c>
+      <c r="F115" s="4" t="n">
+        <v>26771.5</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2866,15 +3442,20 @@
           <t>4393720604471</t>
         </is>
       </c>
-      <c r="C116" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>17321.5</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 591410 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E116" s="4" t="n">
         <v>17321.5</v>
       </c>
+      <c r="F116" s="4" t="n">
+        <v>17321.5</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2887,15 +3468,20 @@
           <t>4393720601203</t>
         </is>
       </c>
-      <c r="C117" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D117" s="4" t="n">
-        <v>20471.5</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 59411 Direct Drive Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E117" s="4" t="n">
         <v>20471.5</v>
       </c>
+      <c r="F117" s="4" t="n">
+        <v>20471.5</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2908,15 +3494,20 @@
           <t>4393720605737</t>
         </is>
       </c>
-      <c r="C118" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>17321.5</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WM 601411 Inverter Steam Grey</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E118" s="4" t="n">
         <v>17321.5</v>
       </c>
+      <c r="F118" s="4" t="n">
+        <v>17321.5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -2929,15 +3520,20 @@
           <t>4393720600404</t>
         </is>
       </c>
-      <c r="C119" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>19596.5</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 45148 Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E119" s="4" t="n">
         <v>19596.5</v>
       </c>
+      <c r="F119" s="4" t="n">
+        <v>19596.5</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2950,15 +3546,20 @@
           <t>4393720605249</t>
         </is>
       </c>
-      <c r="C120" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>20471.5</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 4828 Inverter Steam Grey</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E120" s="4" t="n">
         <v>20471.5</v>
       </c>
+      <c r="F120" s="4" t="n">
+        <v>20471.5</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -2971,15 +3572,20 @@
           <t>4393720606215</t>
         </is>
       </c>
-      <c r="C121" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D121" s="4" t="n">
-        <v>20471.5</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 61211 D Inverter Steam Champagne</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E121" s="4" t="n">
         <v>20471.5</v>
       </c>
+      <c r="F121" s="4" t="n">
+        <v>20471.5</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -2992,15 +3598,20 @@
           <t>4393720471059</t>
         </is>
       </c>
-      <c r="C122" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>19596.5</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 6148 DC Inverter Steam</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E122" s="4" t="n">
         <v>19596.5</v>
       </c>
+      <c r="F122" s="4" t="n">
+        <v>19596.5</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3013,15 +3624,20 @@
           <t>4393720450399</t>
         </is>
       </c>
-      <c r="C123" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D123" s="4" t="n">
-        <v>18721.5</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Стиральная машина Weissgauff WMD 6160 D</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E123" s="4" t="n">
         <v>18721.5</v>
       </c>
+      <c r="F123" s="4" t="n">
+        <v>18721.5</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3034,15 +3650,20 @@
           <t>4393720610298</t>
         </is>
       </c>
-      <c r="C124" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" s="4" t="n">
-        <v>11896.5</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 486 Compact Air</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E124" s="4" t="n">
         <v>11896.5</v>
       </c>
+      <c r="F124" s="4" t="n">
+        <v>11896.5</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3055,15 +3676,20 @@
           <t>4640563531595</t>
         </is>
       </c>
-      <c r="C125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D125" s="4" t="n">
-        <v>12596.5</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 486 DW Compact Smart Dry</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E125" s="4" t="n">
         <v>12596.5</v>
       </c>
+      <c r="F125" s="4" t="n">
+        <v>12596.5</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3076,15 +3702,20 @@
           <t>4393720610311</t>
         </is>
       </c>
-      <c r="C126" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D126" s="4" t="n">
-        <v>11371.5</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 528 D AirVent</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E126" s="4" t="n">
         <v>11371.5</v>
       </c>
+      <c r="F126" s="4" t="n">
+        <v>11371.5</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3097,15 +3728,20 @@
           <t>4393720605508</t>
         </is>
       </c>
-      <c r="C127" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D127" s="4" t="n">
-        <v>14171.5</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 547C</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E127" s="4" t="n">
         <v>14171.5</v>
       </c>
+      <c r="F127" s="4" t="n">
+        <v>14171.5</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3118,15 +3754,20 @@
           <t>4393720467670</t>
         </is>
       </c>
-      <c r="C128" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" s="4" t="n">
-        <v>14871.5</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 6128 D</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E128" s="4" t="n">
         <v>14871.5</v>
       </c>
+      <c r="F128" s="4" t="n">
+        <v>14871.5</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3139,13 +3780,18 @@
           <t>4640213441168</t>
         </is>
       </c>
-      <c r="C129" s="3" t="n">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Сушильная машина Weissgauff WD 6128 D Silver</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D129" s="4" t="n">
+      <c r="E129" s="4" t="n">
         <v>16446.5</v>
       </c>
-      <c r="E129" s="4" t="n">
+      <c r="F129" s="4" t="n">
         <v>32893</v>
       </c>
     </row>
@@ -3160,15 +3806,20 @@
           <t>4393720477433</t>
         </is>
       </c>
-      <c r="C130" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D130" s="4" t="n">
-        <v>37796.5</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WFD 450 Built-in Inverter NoFrost Dark Inox</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E130" s="4" t="n">
         <v>37796.5</v>
       </c>
+      <c r="F130" s="4" t="n">
+        <v>37796.5</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3181,15 +3832,20 @@
           <t>4393720607427</t>
         </is>
       </c>
-      <c r="C131" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" s="4" t="n">
-        <v>4371.5</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WR-046 Defrost Black</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E131" s="4" t="n">
         <v>4371.5</v>
       </c>
+      <c r="F131" s="4" t="n">
+        <v>4371.5</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3202,15 +3858,20 @@
           <t>4393720607434</t>
         </is>
       </c>
-      <c r="C132" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" s="4" t="n">
-        <v>4371.5</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WR-046 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E132" s="4" t="n">
         <v>4371.5</v>
       </c>
+      <c r="F132" s="4" t="n">
+        <v>4371.5</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3223,13 +3884,18 @@
           <t>4670239260740</t>
         </is>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1180 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D133" s="4" t="n">
+      <c r="E133" s="4" t="n">
         <v>9446.5</v>
       </c>
-      <c r="E133" s="4" t="n">
+      <c r="F133" s="4" t="n">
         <v>18893</v>
       </c>
     </row>
@@ -3244,15 +3910,20 @@
           <t>4670239260177</t>
         </is>
       </c>
-      <c r="C134" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D134" s="4" t="n">
-        <v>10496.5</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 1300 Defrost Dark Grey</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E134" s="4" t="n">
         <v>10496.5</v>
       </c>
+      <c r="F134" s="4" t="n">
+        <v>10496.5</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3265,15 +3936,20 @@
           <t>4670239260863</t>
         </is>
       </c>
-      <c r="C135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" s="4" t="n">
-        <v>10496.5</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 145 DeFrost Black</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E135" s="4" t="n">
         <v>10496.5</v>
       </c>
+      <c r="F135" s="4" t="n">
+        <v>10496.5</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3286,15 +3962,20 @@
           <t>4393720608615</t>
         </is>
       </c>
-      <c r="C136" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" s="4" t="n">
-        <v>10496.5</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 145 DeFrost Inox</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E136" s="4" t="n">
         <v>10496.5</v>
       </c>
+      <c r="F136" s="4" t="n">
+        <v>10496.5</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3307,15 +3988,20 @@
           <t>4393720608622</t>
         </is>
       </c>
-      <c r="C137" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" s="4" t="n">
-        <v>10146.5</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 145 DeFrost White</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E137" s="4" t="n">
         <v>10146.5</v>
       </c>
+      <c r="F137" s="4" t="n">
+        <v>10146.5</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3328,15 +4014,20 @@
           <t>4393720603368</t>
         </is>
       </c>
-      <c r="C138" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" s="4" t="n">
-        <v>21871.5</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 185 Total NoFrost Inverter Beige Glass</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E138" s="4" t="n">
         <v>21871.5</v>
       </c>
+      <c r="F138" s="4" t="n">
+        <v>21871.5</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3349,15 +4040,20 @@
           <t>4393720477501</t>
         </is>
       </c>
-      <c r="C139" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D139" s="4" t="n">
-        <v>21871.5</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 185 Total NoFrost Inverter Black Glass</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E139" s="4" t="n">
         <v>21871.5</v>
       </c>
+      <c r="F139" s="4" t="n">
+        <v>21871.5</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3370,13 +4066,18 @@
           <t>4393720603429</t>
         </is>
       </c>
-      <c r="C140" s="3" t="n">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2000 Total NoFrost Inverter Bru Steel Glass</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D140" s="4" t="n">
+      <c r="E140" s="4" t="n">
         <v>23621.5</v>
       </c>
-      <c r="E140" s="4" t="n">
+      <c r="F140" s="4" t="n">
         <v>47243</v>
       </c>
     </row>
@@ -3391,15 +4092,20 @@
           <t>4393720603412</t>
         </is>
       </c>
-      <c r="C141" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D141" s="4" t="n">
-        <v>23621.5</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK 2000 Total NoFrost Inverter Rock Glass</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E141" s="4" t="n">
         <v>23621.5</v>
       </c>
+      <c r="F141" s="4" t="n">
+        <v>23621.5</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -3412,15 +4118,20 @@
           <t>4640213440444</t>
         </is>
       </c>
-      <c r="C142" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" s="4" t="n">
-        <v>7871.5</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK-85 Defrost Grey</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E142" s="4" t="n">
         <v>7871.5</v>
       </c>
+      <c r="F142" s="4" t="n">
+        <v>7871.5</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3433,15 +4144,20 @@
           <t>4640213440512</t>
         </is>
       </c>
-      <c r="C143" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D143" s="4" t="n">
-        <v>7696.5</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRK-85 Defrost White</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E143" s="4" t="n">
         <v>7696.5</v>
       </c>
+      <c r="F143" s="4" t="n">
+        <v>7696.5</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3454,15 +4170,20 @@
           <t>4393720464006</t>
         </is>
       </c>
-      <c r="C144" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" s="4" t="n">
-        <v>22046.5</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRKI 178 Total NoFrost</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E144" s="4" t="n">
         <v>22046.5</v>
       </c>
+      <c r="F144" s="4" t="n">
+        <v>22046.5</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3475,15 +4196,20 @@
           <t>4393720477747</t>
         </is>
       </c>
-      <c r="C145" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D145" s="4" t="n">
-        <v>28346.5</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRKI 195 WLF</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E145" s="4" t="n">
         <v>28346.5</v>
       </c>
+      <c r="F145" s="4" t="n">
+        <v>28346.5</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3496,18 +4222,23 @@
           <t>4393720450894</t>
         </is>
       </c>
-      <c r="C146" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D146" s="4" t="n">
-        <v>29746.5</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Холодильник Weissgauff WRKI 195 WNF</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="E146" s="4" t="n">
         <v>29746.5</v>
       </c>
+      <c r="F146" s="4" t="n">
+        <v>29746.5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E146"/>
+  <autoFilter ref="A1:F146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>